--- a/artfynd/A 61212-2025 artfynd.xlsx
+++ b/artfynd/A 61212-2025 artfynd.xlsx
@@ -1397,12 +1397,7 @@
         <v>121497089</v>
       </c>
       <c r="B7" t="n">
-        <v>57510</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58013</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1436,7 +1431,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1490,7 +1485,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan!</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 61212-2025 artfynd.xlsx
+++ b/artfynd/A 61212-2025 artfynd.xlsx
@@ -1397,7 +1397,7 @@
         <v>121497089</v>
       </c>
       <c r="B7" t="n">
-        <v>58013</v>
+        <v>58021</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 61212-2025 artfynd.xlsx
+++ b/artfynd/A 61212-2025 artfynd.xlsx
@@ -1397,7 +1397,7 @@
         <v>121497089</v>
       </c>
       <c r="B7" t="n">
-        <v>58021</v>
+        <v>58022</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 61212-2025 artfynd.xlsx
+++ b/artfynd/A 61212-2025 artfynd.xlsx
@@ -1397,7 +1397,7 @@
         <v>121497089</v>
       </c>
       <c r="B7" t="n">
-        <v>58022</v>
+        <v>58023</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 61212-2025 artfynd.xlsx
+++ b/artfynd/A 61212-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121497217</v>
+        <v>121497211</v>
       </c>
       <c r="B2" t="n">
-        <v>90746</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,25 +686,33 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -722,10 +725,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>504840</v>
+        <v>504869</v>
       </c>
       <c r="R2" t="n">
-        <v>7010987</v>
+        <v>7011055</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -797,12 +800,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Liggande stam och högstubbe av en knäckt gran. # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -820,70 +823,60 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121496472</v>
+        <v>121548388</v>
       </c>
       <c r="B3" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gnagmyrmon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504851</v>
+        <v>504891</v>
       </c>
       <c r="R3" t="n">
-        <v>7011045</v>
+        <v>7011076</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -920,7 +913,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Minst 10 st. skott/stjälkar och 2 st. vinterståndare av knärot inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,12 +928,32 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrsumpskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen är här utdikad och här finns äldre spår av röjning.</t>
+          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen här är utdikad och här finns äldre spår av röjning.</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Harticka i två stammar. # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -958,73 +971,55 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121497010</v>
+        <v>121497118</v>
       </c>
       <c r="B4" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gnagmyrmon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>504920</v>
+        <v>504876</v>
       </c>
       <c r="R4" t="n">
-        <v>7011117</v>
+        <v>7011032</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1058,7 +1053,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Minst 11 st. skott/stjälkar och 1 st. vinterståndare av knärot inom ca 0,5 m2 yta. Fyndplatsen besöktes när stor del av marken var snötäckt. Troligen finns här fler skott av knärot. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1079,6 +1074,26 @@
       <c r="AI4" t="inlineStr">
         <is>
           <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen är här utdikad och här finns äldre spår av röjning.</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1096,60 +1111,60 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121497118</v>
+        <v>121548338</v>
       </c>
       <c r="B5" t="n">
-        <v>90728</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gnagmyrmon, Jmt</t>
+          <t>Gnagmyrmon, Svanamyren, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504876</v>
+        <v>504834</v>
       </c>
       <c r="R5" t="n">
-        <v>7011032</v>
+        <v>7011084</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1192,7 +1207,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1218,12 +1232,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1241,15 +1255,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121497211</v>
+        <v>121497089</v>
       </c>
       <c r="B6" t="n">
-        <v>90724</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1257,52 +1266,53 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gnagmyrmon, Jmt</t>
+          <t>Gnagmyrmon, Svanamyren, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>504869</v>
+        <v>504833</v>
       </c>
       <c r="R6" t="n">
-        <v>7011055</v>
+        <v>7010908</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1336,7 +1346,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
+          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan!</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1345,7 +1355,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1357,26 +1366,6 @@
       <c r="AI6" t="inlineStr">
         <is>
           <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen här är utdikad och här finns äldre spår av röjning.</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1394,46 +1383,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121497089</v>
+        <v>121496472</v>
       </c>
       <c r="B7" t="n">
-        <v>58043</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1441,17 +1434,17 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gnagmyrmon, Svanamyren, Lit, Jmt</t>
+          <t>Gnagmyrmon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>504833</v>
+        <v>504851</v>
       </c>
       <c r="R7" t="n">
-        <v>7010908</v>
+        <v>7011045</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1485,7 +1478,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan!</t>
+          <t>Minst 10 st. skott/stjälkar och 2 st. vinterståndare av knärot inom ca 1 m2 yta. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1494,6 +1487,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1504,7 +1498,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen här är utdikad och här finns äldre spår av röjning.</t>
+          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen är här utdikad och här finns äldre spår av röjning.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1522,65 +1516,65 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121548388</v>
+        <v>121497010</v>
       </c>
       <c r="B8" t="n">
-        <v>90724</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gnagmyrmon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>504891</v>
+        <v>504920</v>
       </c>
       <c r="R8" t="n">
-        <v>7011076</v>
+        <v>7011117</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1617,7 +1611,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
+          <t>Minst 11 st. skott/stjälkar och 1 st. vinterståndare av knärot inom ca 0,5 m2 yta. Fyndplatsen besöktes när stor del av marken var snötäckt. Troligen finns här fler skott av knärot. Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1632,32 +1626,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrsumpskog</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen här är utdikad och här finns äldre spår av röjning.</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Harticka i två stammar. # Picea abies</t>
+          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen är här utdikad och här finns äldre spår av röjning.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1672,155 +1646,6 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>121548338</v>
-      </c>
-      <c r="B9" t="n">
-        <v>57373</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Gnagmyrmon, Svanamyren, Lit, Jmt</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>504834</v>
-      </c>
-      <c r="R9" t="n">
-        <v>7011084</v>
-      </c>
-      <c r="S9" t="n">
-        <v>5</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Lit</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2024-12-06</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Obs! Fyndplatsen finns inom en avverkningsanmälan med beteckning A 54508-2024.</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Barrsumpskog</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Barrdominerad sumpskog med bitvis gott om stående och liggande död ved i olika dimensioner. Träd med socklar och spår av hackspettar. Sumpskogen är här utdikad och här finns äldre spår av röjning.</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61212-2025 artfynd.xlsx
+++ b/artfynd/A 61212-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -820,6 +825,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121497211</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -968,6 +978,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121548388</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1108,6 +1123,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121497118</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1252,6 +1272,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121548338</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1380,6 +1405,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121497089</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1513,6 +1543,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121496472</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1646,8 +1681,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121497010</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>